--- a/output/HS_Code_Summary_ADITEG_CZ26009365.xlsx
+++ b/output/HS_Code_Summary_ADITEG_CZ26009365.xlsx
@@ -888,12 +888,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>JSD 3 – FOC položka (kompenzace obj. 80615829)</t>
+          <t>JSD 3 – kontejner MSKU5698651 (FOC položka, kompenzace obj. 80615829)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>MSKU5698651 (fyzicky v témže kontejneru jako JSD 1)</t>
+          <t>MSKU5698651</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -941,7 +941,7 @@
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>MEZISOUČET JSD 3 – FOC položka (kompenzace obj. 80615829)</t>
+          <t>MEZISOUČET JSD 3 – kontejner MSKU5698651 (FOC položka, kompenzace obj. 80615829)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JSD 3 – FOC položka. POZOR: jede v kontejneru MSKU5698651 spolu s JSD 1, není to samostatný kontejner.</t>
+          <t>JSD 3 – FOC položka, kontejner MSKU5698651 (stejný kontejner jako JSD 1, dělí se mezi obě prohlášení).</t>
         </is>
       </c>
       <c r="G14" s="20" t="n"/>
@@ -2034,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A105"/>
+  <dimension ref="A1:A109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -2123,7 +2123,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JSD 3 – FOC položka art. 0230238 (kompenzace obj. 80615829):</t>
+          <t>JSD 3 – kontejner MSKU5698651, FOC položka art. 0230238 (kompenzace obj. 80615829):</t>
         </is>
       </c>
     </row>
@@ -2147,475 +2147,475 @@
     <row r="17">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>⚠ POZOR – FOC ZBOŽÍ NENÍ SAMOSTATNÝ KONTEJNER</t>
+          <t>⚠ KONTEJNER U FOC POLOŽKY (JSD 3) = MSKU5698651</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pravidlo „1 JSD = 1 kontejner“ platí pro JSD 1 a JSD 2. FOC položka (JSD 3) je fyzicky naložena</t>
+          <t>Na JSD 3 se do kolonky kontejneru uvádí MSKU5698651 – NE druhý kontejner a NE prázdná kolonka.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>v kontejneru MSKU5698651, tedy ve stejném kontejneru jako zboží na JSD 1.</t>
+          <t>Doklad: packing list 1 obsahuje FOC položku art. 0230238 (60 rolí, NW 2 700 kg, GW 2 720 kg)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kontejner MSKU5698651 se proto dělí mezi dvě celní prohlášení:</t>
+          <t>a jeho patička uvádí: MSKU5698651/CN6923658/20'GP/357PACKAGES/22470KGS/25CBM.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">        JSD 1: 297 ks / GW 19 750 kg  +  JSD 3: 60 ks / GW 2 720 kg  =  357 ks / 22 470 kg</t>
+          <t>Celkem 357 kusů na PL1 zahrnuje i těchto 60 FOC rolí – FOC zboží tedy jede v tomto kontejneru.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>→ To přesně odpovídá packing listu 1 a údaji na B/L pro tento kontejner.</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>→ Hmotnost kontejneru MSKU5698651 tedy NEBUDE souhlasit s JSD 1 samotným – je nutné uvádět</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pravidlo „1 JSD = 1 kontejner“ proto platí beze zbytku jen pro JSD 2. Kontejner MSKU5698651</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   obě JSD společně a v popisu zboží na obou uvést, že jde o dělený kontejner.</t>
+          <t>se dělí mezi dvě celní prohlášení (JSD 1 a JSD 3), obě na stejné číslo kontejneru:</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kontejner MRKU9108387 = celé JSD 2, 172 ks / 22 420 kg – souhlasí bez dělení.</t>
+          <t xml:space="preserve">        JSD 1: 297 ks / GW 19 750 kg  +  JSD 3: 60 ks / GW 2 720 kg  =  357 ks / 22 470 kg</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>→ To přesně odpovídá packing listu 1 i údaji na B/L pro tento kontejner.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>KONTROLA PROTI B/L AHD26060517</t>
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>→ Hmotnost kontejneru NEBUDE souhlasit s JSD 1 samotným – v popisu zboží na JSD 1 i JSD 3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t xml:space="preserve">   uvést, že jde o dělený kontejner, a obě prohlášení podat společně.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kontejner MRKU9108387 = celé JSD 2, 172 ks / 22 420 kg – souhlasí bez dělení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>KONTROLA PROTI B/L AHD26060517</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>B/L: 2 x 20'GP, 529 PACKAGES, 44 890,000 KGS, 50,000 CBM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="29" t="inlineStr">
-        <is>
-          <t>✓ Počet kusů: 297 + 172 + 60 = 529 ks – souhlasí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>✓ Hrubá hmotnost: 19 750 + 22 420 + 2 720 = 44 890 kg – souhlasí na kilogram.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>✓ Kontejner MSKU5698651: 357 ks / 22 470 kg – souhlasí s B/L i PL1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>✓ Kontejner MRKU9108387: 172 ks / 22 420 kg – souhlasí s B/L i PL2.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
+          <t>✓ Počet kusů: 297 + 172 + 60 = 529 ks – souhlasí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>✓ Hrubá hmotnost: 19 750 + 22 420 + 2 720 = 44 890 kg – souhlasí na kilogram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>✓ Kontejner MSKU5698651: 357 ks / 22 470 kg – souhlasí s B/L i PL1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>✓ Kontejner MRKU9108387: 172 ks / 22 420 kg – souhlasí s B/L i PL2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
           <t>✓ Součty faktur: 10 503,01 + 13 651,81 = 24 154,82 USD (bez FOC).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>CELNÍ HODNOTA – pravidlo „Total“</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Použity částky ze sloupce „Total amount usd“ na fakturách. Žádná obchodní sleva na této zásilce není,</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>hodnoty před/po slevě se tedy neuvádějí. Kontrolní součty JSD 1 a JSD 2 odpovídají řádku „Total“ faktur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>FOC položka nemá na faktuře hodnotu (0,00) – celní hodnota dopočtena, viz JSD 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>⚠ SAZEBNÍ ZAŘAZENÍ – POUŽITO PRAVIDLO CCT/VPV KN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V podkladech (faktury, packing listy, B/L) NENÍ uveden žádný HS kód – B/L popisuje zboží jen jako</t>
+          <t>hodnoty před/po slevě se tedy neuvádějí. Kontrolní součty JSD 1 a JSD 2 odpovídají řádku „Total“ faktur.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>„RUBBER SHEET“. Oba níže uvedené kódy jsem odvodila pravidlem CCT/VPV KN podle</t>
+          <t>FOC položka nemá na faktuře hodnotu (0,00) – celní hodnota dopočtena, viz JSD 3.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>reference/Common_Customs_Tariff_EU_CZ.pptx. Takto zařazené položky:</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>⚠ SAZEBNÍ ZAŘAZENÍ – POUŽITO PRAVIDLO CCT/VPV KN</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A) 4008 21 90 – art. 0231268, 0230179, 0231419, 0230264, 0234614, 0230540, 0232061,</t>
+          <t>V podkladech (faktury, packing listy, B/L) NENÍ uveden žádný HS kód – B/L popisuje zboží jen jako</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   0232184, 0231843, 0231842, 0230301</t>
+          <t>„RUBBER SHEET“. Oba níže uvedené kódy jsem odvodila pravidlem CCT/VPV KN podle</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CO TO JE? Desky / pásy z vulkanizovaného kaučuku v rolích, černé, 65 ±5 ShA, 2-3 a 7-8 MPa, tl. 3–20 mm.</t>
+          <t>reference/Common_Customs_Tariff_EU_CZ.pptx. Takto zařazené položky:</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Z ČEHO TO JE? Vulkanizovaný nelehčený kaučuk SBR / EPDM; u tří položek 1 textilní vložka (fabric) jako výztuž.</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   K ČEMU SLOUŽÍ? Technická pryž – těsnění, obklady, podložky; polotovar dodávaný v rolích k dalšímu zpracování.</t>
+          <t>A) 4008 21 90 – art. 0231268, 0230179, 0231419, 0230264, 0234614, 0230540, 0232061,</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Postup: TŘÍDA VII (plasty, kaučuk a pryž) → kapitola 40 → úvodní poznámky ke kap. 40 zboží nevylučují →</t>
+          <t xml:space="preserve">   0232184, 0231843, 0231842, 0230301</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   číslo 4008 „Desky, listy, pásy, tyče a profily z vulkanizovaného kaučuku, jiného než tvrdého kaučuku“ →</t>
+          <t xml:space="preserve">   CO TO JE? Desky / pásy z vulkanizovaného kaučuku v rolích, černé, 65 ±5 ShA, 2-3 a 7-8 MPa, tl. 3–20 mm.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">   podpoložka 4008 21 (z nelehčeného kaučuku – desky, listy a pásy) → KN 4008 21 90 (ostatní). VPV 1 a VPV 6.</t>
+          <t xml:space="preserve">   Z ČEHO TO JE? Vulkanizovaný nelehčený kaučuk SBR / EPDM; u tří položek 1 textilní vložka (fabric) jako výztuž.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Textilní vložka: podle VPV 3(b) dává podstatný charakter kaučuk (výrazně převažuje hmotnostně, vložka</t>
+          <t xml:space="preserve">   K ČEMU SLOUŽÍ? Technická pryž – těsnění, obklady, podložky; polotovar dodávaný v rolích k dalšímu zpracování.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   plní pouze vyztužovací funkci) → zůstává v kap. 40, nikoli v kap. 59.</t>
+          <t xml:space="preserve">   Postup: TŘÍDA VII (plasty, kaučuk a pryž) → kapitola 40 → úvodní poznámky ke kap. 40 zboží nevylučují →</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   číslo 4008 „Desky, listy, pásy, tyče a profily z vulkanizovaného kaučuku, jiného než tvrdého kaučuku“ →</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B) 4016 91 00 – art. 0230559, 0230564, 0230238</t>
+          <t xml:space="preserve">   podpoložka 4008 21 (z nelehčeného kaučuku – desky, listy a pásy) → KN 4008 21 90 (ostatní). VPV 1 a VPV 6.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CO TO JE? Podlahové rohože z pryže – kamínková deska, kamínková deska speciál, rýhovaná deska.</t>
+          <t xml:space="preserve">   Textilní vložka: podle VPV 3(b) dává podstatný charakter kaučuk (výrazně převažuje hmotnostně, vložka</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Z ČEHO TO JE? Vulkanizovaný nelehčený kaučuk (pryž).</t>
+          <t xml:space="preserve">   plní pouze vyztužovací funkci) → zůstává v kap. 40, nikoli v kap. 59.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   K ČEMU SLOUŽÍ? Podlahová krytina / rohož – stájové a protiskluzové podlahy (Horse Rubber mat, Stable Mat).</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Postup: TŘÍDA VII → kapitola 40 → číslo 4016 „Ostatní výrobky z vulkanizovaného kaučuku, jiného než</t>
+          <t>B) 4016 91 00 – art. 0230559, 0230564, 0230238</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">   tvrdého kaučuku“ → KN 4016 91 00 „Podlahové krytiny a rohože“. Podle VPV 3(a) má konkrétnější popis</t>
+          <t xml:space="preserve">   CO TO JE? Podlahové rohože z pryže – kamínková deska, kamínková deska speciál, rýhovaná deska.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (hotová podlahová krytina) přednost před obecným číslem 4008 pro desky a pásy.</t>
+          <t xml:space="preserve">   Z ČEHO TO JE? Vulkanizovaný nelehčený kaučuk (pryž).</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   K ČEMU SLOUŽÍ? Podlahová krytina / rohož – stájové a protiskluzové podlahy (Horse Rubber mat, Stable Mat).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>⚠ NEJISTOTA – DOPORUČUJI KONZULTOVAT</t>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Postup: TŘÍDA VII → kapitola 40 → číslo 4016 „Ostatní výrobky z vulkanizovaného kaučuku, jiného než</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1) Hranice 4008 vs. 4016 u art. 0230559 (3 mm Kamínková deska, dodávaná v roli 1,2 × 10 m) – rozměr</t>
+          <t xml:space="preserve">   tvrdého kaučuku“ → KN 4016 91 00 „Podlahové krytiny a rohože“. Podle VPV 3(a) má konkrétnější popis</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">   odpovídá spíše roli materiálu než hotové rohoži. Zařazeno do 4016 91 00 podle účelu (stájová rohož).</t>
+          <t xml:space="preserve">   (hotová podlahová krytina) přednost před obecným číslem 4008 pro desky a pásy.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2) Položky s textilní vložkou – hranice kap. 40 vs. 5906. Zařazeno do 4008 21 90.</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>→ Před podáním doporučuji potvrdit v TARIC, případně konzultovat tarifní tým: customs.tariff@mauriceward.com</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>⚠ NEJISTOTA – DOPORUČUJI KONZULTOVAT</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (tento krok jsem zatím neprovedla – rozhodni prosím Ty).</t>
+          <t>1) Hranice 4008 vs. 4016 u art. 0230559 (3 mm Kamínková deska, dodávaná v roli 1,2 × 10 m) – rozměr</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   odpovídá spíše roli materiálu než hotové rohoži. Zařazeno do 4016 91 00 podle účelu (stájová rohož).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>⚠ PREFERENČNÍ PŮVOD A REX – OBOJÍ CHYBÍ</t>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2) Položky s textilní vložkou – hranice kap. 40 vs. 5906. Zařazeno do 4008 21 90.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>PREFERENČNÍ VĚTA: NENÍ uvedena v žádném z dokladů. Zkontrolovány obě faktury, oba packing listy i B/L.</t>
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>→ Před podáním doporučuji potvrdit v TARIC, případně konzultovat tarifní tým: customs.tariff@mauriceward.com</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>REX ČÍSLO: NENÍ na žádné z faktur uvedeno. Faktury neobsahují číslo registrovaného vývozce</t>
+          <t xml:space="preserve">   (tento krok jsem zatím neprovedla – rozhodni prosím Ty).</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>ani jiné číslo celního povolení vývozce.</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Země původu: Čína (CN). EU nemá s ČLR dohodu o preferenčním obchodu, preferenční sazba proto</t>
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>⚠ PREFERENČNÍ PŮVOD A REX – OBOJÍ CHYBÍ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>není možná ani při doložení prohlášení – uplatní se standardní třetizemní clo (erga omnes).</t>
+          <t>PREFERENČNÍ VĚTA: NENÍ uvedena v žádném z dokladů. Zkontrolovány obě faktury, oba packing listy i B/L.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>→ Sazbu k oběma HS kódům ověřit v TARIC k datu propuštění zboží.</t>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>REX ČÍSLO: NENÍ na žádné z faktur uvedeno. Faktury neobsahují číslo registrovaného vývozce</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ani jiné číslo celního povolení vývozce.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>CBAM</t>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Země původu: Čína (CN). EU nemá s ČLR dohodu o preferenčním obchodu, preferenční sazba proto</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>není možná ani při doložení prohlášení – uplatní se standardní třetizemní clo (erga omnes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="inlineStr">
+        <is>
+          <t>→ Sazbu k oběma HS kódům ověřit v TARIC k datu propuštění zboží.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
+          <t>CBAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>Zásilka NEOBSAHUJE žádnou CBAM položku – kaučuk a pryž (kapitola 40) nejsou v příloze I nařízení CBAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>(CBAM = cement, elektřina, hnojiva, železo a ocel, hliník, vodík). Kód Y128/Y238/Y137 se na žádné JSD neuvádí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Pro pořádek prověřeno v reference/CBAM_receivers_CZ.xlsx (list List1):</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>⚠ ADITEG s.r.o. (EORI CZ26905710) V REGISTRU NENÍ – ani podle názvu firmy, ani podle EORI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="29" t="inlineStr">
-        <is>
-          <t>→ Pro tuto zásilku to nevadí (žádné CBAM zboží). Pokud by ADITEG někdy dovážel CBAM zboží, je nutné</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">   nejdřív zjistit jeho CBAM status a doplnit ho do registru. Status nedomýšlet.</t>
+          <t>(CBAM = cement, elektřina, hnojiva, železo a ocel, hliník, vodík). Kód Y128/Y238/Y137 se na žádné JSD neuvádí.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Pro pořádek prověřeno v reference/CBAM_receivers_CZ.xlsx (list List1):</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="30" t="inlineStr">
-        <is>
-          <t>ANTIDUMPING</t>
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>⚠ ADITEG s.r.o. (EORI CZ26905710) V REGISTRU NENÍ – ani podle názvu firmy, ani podle EORI.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Pro desky a rohože z vulkanizovaného kaučuku (4008 21, 4016 91) původem z ČLR nebylo zjištěno</t>
+      <c r="A88" s="29" t="inlineStr">
+        <is>
+          <t>→ Pro tuto zásilku to nevadí (žádné CBAM zboží). Pokud by ADITEG někdy dovážel CBAM zboží, je nutné</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>žádné platné antidumpingové ani vyrovnávací opatření. Ověřit v TARIC k datu podání JSD.</t>
+          <t xml:space="preserve">   nejdřív zjistit jeho CBAM status a doplnit ho do registru. Status nedomýšlet.</t>
         </is>
       </c>
     </row>
@@ -2625,21 +2625,21 @@
     <row r="91">
       <c r="A91" s="30" t="inlineStr">
         <is>
-          <t>INCOTERM</t>
+          <t>ANTIDUMPING</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FOB Xingang (Tianjin), Čína – dle obou faktur. Na B/L „FREIGHT COLLECT“, což je s FOB v souladu.</t>
+          <t>Pro desky a rohože z vulkanizovaného kaučuku (4008 21, 4016 91) původem z ČLR nebylo zjištěno</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29" t="inlineStr">
-        <is>
-          <t>→ Do celní hodnoty je nutno připočíst náklady na přepravu a pojištění do místa vstupu do EU.</t>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>žádné platné antidumpingové ani vyrovnávací opatření. Ověřit v TARIC k datu podání JSD.</t>
         </is>
       </c>
     </row>
@@ -2647,73 +2647,97 @@
       <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="28" t="inlineStr">
-        <is>
-          <t>⚠ NESROVNALOST V PODKLADECH – art. 0230564</t>
+      <c r="A95" s="30" t="inlineStr">
+        <is>
+          <t>INCOTERM</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>FOB Xingang (Tianjin), Čína – dle obou faktur. Na B/L „FREIGHT COLLECT“, což je s FOB v souladu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="29" t="inlineStr">
+        <is>
+          <t>→ Do celní hodnoty je nutno připočíst náklady na přepravu a pojištění do místa vstupu do EU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>⚠ NESROVNALOST V PODKLADECH – art. 0230564</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>Faktura uvádí „17 mm Kamínková deska spec.“, packing list v popisu „12 mm Kamínková deska spec.“,</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>přičemž rozměr je v obou dokladech 1,22 x 1,83 m x 17 mm. V tabulce je použit popis z faktury (17 mm).</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="29" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="29" t="inlineStr">
         <is>
           <t>→ Vyjasnit s odesílatelem před podáním – údaj jde do popisu zboží v kolonce 31.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Kontrola množství: 446,52 m² / (1,22 × 1,83 m) = přesně 200 ks – souhlasí s packing listem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="27" t="inlineStr">
-        <is>
-          <t>POZNÁMKA K POPISU ZBOŽÍ A KE SLUČOVÁNÍ</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Popisy v tabulce jsou převzaty doslovně z faktur (česky), bez úprav a bez přeformulování.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Kontrola množství: 446,52 m² / (1,22 × 1,83 m) = přesně 200 ks – souhlasí s packing listem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>POZNÁMKA K POPISU ZBOŽÍ A KE SLUČOVÁNÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Popisy v tabulce jsou převzaty doslovně z faktur (česky), bez úprav a bez přeformulování.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>Položky jsou sloučeny na unikátní HS kódy v rámci každého JSD. Stejný HS kód 4008 21 90 je na JSD 1</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>i na JSD 2 samostatně – jde o dvě různá celní prohlášení, nelze je slučovat napříč JSD.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Odesílatel je u celé zásilky jeden (Qingdao Conet), dělení podle odesílatele proto nebylo potřeba.</t>
         </is>

--- a/output/HS_Code_Summary_ADITEG_CZ26009365.xlsx
+++ b/output/HS_Code_Summary_ADITEG_CZ26009365.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,9 @@
 0230179 – SBR 65 +/- 5 Sh.černá, 2-3 MPa 5 mm x 1.200 x 10.000 mm
 0231419 – SBR 65 +/- 5 Sh.černá, 2-3 MPa 6 mm x 2.000 x 10.000 mm
 0230264 – SBR 65 +/- 5 Sh.černá, 2-3 MPa, 1 vložka(fabric) 10 mm x 1.200 x 10.000 mm
-0234614 – SBR 65 +/-5SHA  černá, 2-3 MPa 8 mm x1.600 x 10.000 mm</t>
+0234614 – SBR 65 +/-5SHA  černá, 2-3 MPa 8 mm x1.600 x 10.000 mm
+0230559 – 3 mm Kamínková deska.(Horse Rubber mat) 3 mm x 1.200 x 10.000 mm
+0230564 – 17 mm Kamínková deska spec.（Round button Stable Mat）Kamínková deska - speciál 1,22 x 1,83 m x 17 mm</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -676,19 +678,19 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1268</v>
+        <v>1786.52</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>91</v>
+        <v>297</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11018</v>
+        <v>19379</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>11220</v>
+        <v>19750</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>5374.71</v>
+        <v>10503.01</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -697,119 +699,61 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>HS kód odvozen pravidlem CCT/VPV KN (v podkladech není uveden) – ověřit v TARIC. U položek s textilní vložkou (0230264, 0232184, 0230301) ověřit hranici vůči kap. 59 (5906).</t>
+          <t>HS kód zadán deklarantem – celá zásilka pod jedním kódem 4008 21 90. V podkladech odesílatele HS kód uveden není.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>MEZISOUČET JSD 1 – kontejner MSKU5698651 (placené zboží)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="7" t="n">
+        <v>1786.52</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>297</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>19379</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>19750</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>10503.01</v>
+      </c>
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Qingdao Conet International Trade Co., Ltd., Qingdao, ČLR</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>JSD 1 – kontejner MSKU5698651 (placené zboží)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>MSKU5698651</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>4016910000</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>0230559 – 3 mm Kamínková deska.(Horse Rubber mat) 3 mm x 1.200 x 10.000 mm
-0230564 – 17 mm Kamínková deska spec.（Round button Stable Mat）Kamínková deska - speciál 1,22 x 1,83 m x 17 mm</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>518.52</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>206</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>8361</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>8530</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>5128.3</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>FOB Xingang (Tianjin), Čína</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>HS kód odvozen pravidlem CCT/VPV KN (v podkladech není uveden) – ověřit v TARIC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>MEZISOUČET JSD 1 – kontejner MSKU5698651 (placené zboží)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="7" t="n">
-        <v>1786.52</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>297</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>19379</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>19750</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>10503.01</v>
-      </c>
-      <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Qingdao Conet International Trade Co., Ltd., Qingdao, ČLR</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>JSD 2 – kontejner MRKU9108387 (placené zboží)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>MRKU9108387</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>4008219000</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>0230540 – EPDM/SBR 65 +/- 5 Sh.černá, 7-8 MPa 5mm x 1.200 x 10.000 mm
 0232061 – SBR 65 +/- 5 Sh. černá, 2-3 MPa 20 mm x 1.400 x 10.000 mm
@@ -820,186 +764,199 @@
 0230301 – EPDM/SBR 65 +/- 5 ShA černá, 2-3 MPa, 1 vložka 8 mm x 1.200 x 10.000 mm</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G4" s="11" t="n">
         <v>2392</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H4" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I4" s="11" t="n">
         <v>22340</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J4" s="11" t="n">
         <v>22420</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K4" s="11" t="n">
         <v>13651.81</v>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>FOB Xingang (Tianjin), Čína</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>HS kód odvozen pravidlem CCT/VPV KN (v podkladech není uveden) – ověřit v TARIC. U položek s textilní vložkou (0230264, 0232184, 0230301) ověřit hranici vůči kap. 59 (5906).</t>
-        </is>
-      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>HS kód zadán deklarantem – celá zásilka pod jedním kódem 4008 21 90. V podkladech odesílatele HS kód uveden není.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>MEZISOUČET JSD 2 – kontejner MRKU9108387 (placené zboží)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="7" t="n">
+        <v>2392</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>172</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>22340</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>22420</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>13651.81</v>
+      </c>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>MEZISOUČET JSD 2 – kontejner MRKU9108387 (placené zboží)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="7" t="n">
-        <v>2392</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>172</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>22340</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>22420</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>13651.81</v>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Qingdao Conet International Trade Co., Ltd., Qingdao, ČLR</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>JSD 3 – kontejner MSKU5698651 (FOC položka, kompenzace obj. 80615829)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>MSKU5698651</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>4008219000</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>0230238 – Fine ribbed mat(Rýhovaná deska - malá) 3mm，1.2X10m</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>1928.45</v>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>FOB Xingang (Tianjin), Čína</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>FOC – na faktuře 0,00 USD. Celní hodnota dopočtena z jednotkové ceny stejného zboží na faktuře: 2,6784 USD/m² × 720 m² = 1 928,448 USD. Odsouhlaseno. HS kód zadán deklarantem – celá zásilka pod jedním kódem 4008 21 90. V podkladech odesílatele HS kód uveden není.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Qingdao Conet International Trade Co., Ltd., Qingdao, ČLR</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>JSD 3 – kontejner MSKU5698651 (FOC položka, kompenzace obj. 80615829)</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>MSKU5698651</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>4016910000</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>0230238 – Fine ribbed mat(Rýhovaná deska - malá) 3mm，1.2X10m</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="n">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>MEZISOUČET JSD 3 – kontejner MSKU5698651 (FOC položka, kompenzace obj. 80615829)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="n">
         <v>720</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="7" t="n">
         <v>2700</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="7" t="n">
         <v>2720</v>
       </c>
-      <c r="K7" s="15" t="n">
+      <c r="K7" s="7" t="n">
         <v>1928.45</v>
       </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>FOB Xingang (Tianjin), Čína</t>
-        </is>
-      </c>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>FOC – na faktuře 0,00 USD. Celní hodnota dopočtena z jednotkové ceny stejného zboží na faktuře: 2,6784 USD/m² × 720 m² = 1 928,448 USD. Odsouhlaseno. HS kód odvozen pravidlem CCT/VPV KN (v podkladech není uveden) – ověřit v TARIC.</t>
-        </is>
-      </c>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>MEZISOUČET JSD 3 – kontejner MSKU5698651 (FOC položka, kompenzace obj. 80615829)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="7" t="n">
-        <v>720</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>2720</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>1928.45</v>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="A8" s="17" t="inlineStr"/>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>CELKEM ZÁSILKA</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="18" t="n">
+        <v>4898.52</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>529</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>44419</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>44890</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>26083.27</v>
+      </c>
+      <c r="L8" s="17" t="inlineStr"/>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>Souhlasí s B/L AHD26060517: 529 PACKAGES / 44 890,000 KGS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>CELKEM ZÁSILKA</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr"/>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="18" t="n">
-        <v>4898.52</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>529</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>44419</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>44890</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>26083.27</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr"/>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>Souhlasí s B/L AHD26060517: 529 PACKAGES / 44 890,000 KGS</t>
-        </is>
-      </c>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
+      <c r="K9" s="20" t="n"/>
     </row>
     <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Legenda:</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="G10" s="20" t="n"/>
       <c r="H10" s="21" t="n"/>
       <c r="I10" s="20" t="n"/>
@@ -1009,10 +966,14 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Legenda:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>🔵 MODRÁ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JSD 1 – kontejner MSKU5698651, placené zboží.</t>
+        </is>
+      </c>
       <c r="G11" s="20" t="n"/>
       <c r="H11" s="21" t="n"/>
       <c r="I11" s="20" t="n"/>
@@ -1022,12 +983,12 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>🔵 MODRÁ</t>
+          <t>🟢 ZELENÁ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JSD 1 – kontejner MSKU5698651, placené zboží.</t>
+          <t>JSD 2 – kontejner MRKU9108387, placené zboží.</t>
         </is>
       </c>
       <c r="G12" s="20" t="n"/>
@@ -1039,12 +1000,12 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>🟢 ZELENÁ</t>
+          <t>🟠 ORANŽOVÁ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JSD 2 – kontejner MRKU9108387, placené zboží.</t>
+          <t>JSD 3 – FOC položka, kontejner MSKU5698651 (stejný kontejner jako JSD 1, dělí se mezi obě prohlášení).</t>
         </is>
       </c>
       <c r="G13" s="20" t="n"/>
@@ -1056,12 +1017,12 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>🟠 ORANŽOVÁ</t>
+          <t>HS kód</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JSD 3 – FOC položka, kontejner MSKU5698651 (stejný kontejner jako JSD 1, dělí se mezi obě prohlášení).</t>
+          <t>Celá zásilka pod jedním kódem 4008 21 90 – zadáno deklarantem. V podkladech odesílatele HS kód není.</t>
         </is>
       </c>
       <c r="G14" s="20" t="n"/>
@@ -1073,12 +1034,12 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>⚠ HS kódy</t>
+          <t>⚠ Preferenční věta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V podkladech NEJSOU uvedeny – odvozeny pravidlem CCT/VPV KN. Viz list „Dokumenty a poznámky“.</t>
+          <t>V dokladech NENÍ. ⚠ REX číslo na fakturách také NENÍ. Původ ČLR → standardní třetizemní clo.</t>
         </is>
       </c>
       <c r="G15" s="20" t="n"/>
@@ -1090,12 +1051,12 @@
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>⚠ Preferenční věta</t>
+          <t>Celní hodnota</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>V dokladech NENÍ. ⚠ REX číslo na fakturách také NENÍ. Původ ČLR → standardní třetizemní clo.</t>
+          <t>Převzata ze sloupce „Total amount usd“ na fakturách. Žádná sleva se neuplatňuje.</t>
         </is>
       </c>
       <c r="G16" s="20" t="n"/>
@@ -1107,12 +1068,12 @@
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>Celní hodnota</t>
+          <t>Popis zboží</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Převzata ze sloupce „Total amount usd“ na fakturách. Žádná sleva se neuplatňuje.</t>
+          <t>Doslovný český popis z faktury, bez úprav.</t>
         </is>
       </c>
       <c r="G17" s="20" t="n"/>
@@ -1124,12 +1085,12 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Popis zboží</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Doslovný český popis z faktury, bez úprav.</t>
+          <t>Netýká se (kapitola 40). ⚠ ADITEG s.r.o. však v registru CBAM chybí – viz poznámky.</t>
         </is>
       </c>
       <c r="G18" s="20" t="n"/>
@@ -1137,23 +1098,6 @@
       <c r="I18" s="20" t="n"/>
       <c r="J18" s="20" t="n"/>
       <c r="K18" s="20" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>CBAM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Netýká se (kapitola 40). ⚠ ADITEG s.r.o. však v registru CBAM chybí – viz poznámky.</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1211,7 +1155,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>HS kód (CCT/VPV KN)</t>
+          <t>HS kód</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1523,7 +1467,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>4016910000</t>
+          <t>4008219000</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
@@ -1573,7 +1517,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>4016910000</t>
+          <t>4008219000</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -1973,7 +1917,7 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>4016910000</t>
+          <t>4008219000</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -2034,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A109"/>
+  <dimension ref="A1:A96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -2318,30 +2262,30 @@
       <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>⚠ SAZEBNÍ ZAŘAZENÍ – POUŽITO PRAVIDLO CCT/VPV KN</t>
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>SAZEBNÍ ZAŘAZENÍ – JEDEN HS KÓD PRO CELOU ZÁSILKU: 4008 21 90</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V podkladech (faktury, packing listy, B/L) NENÍ uveden žádný HS kód – B/L popisuje zboží jen jako</t>
+          <t>Celá zásilka (všechny tři JSD, všech 15 fakturačních položek) je zařazena pod jediný kód</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>„RUBBER SHEET“. Oba níže uvedené kódy jsem odvodila pravidlem CCT/VPV KN podle</t>
+          <t>4008 21 90 – zadáno deklarantem. HS kód není v podkladech odesílatele nikde uveden</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>reference/Common_Customs_Tariff_EU_CZ.pptx. Takto zařazené položky:</t>
+          <t>(faktury, packing listy ani B/L jej neobsahují; B/L popisuje zboží jen jako „RUBBER SHEET“).</t>
         </is>
       </c>
     </row>
@@ -2351,393 +2295,302 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A) 4008 21 90 – art. 0231268, 0230179, 0231419, 0230264, 0234614, 0230540, 0232061,</t>
+          <t>Znění kódu: TŘÍDA VII – kapitola 40 „Kaučuk a výrobky z něj“, číslo 4008 „Desky, listy, pásy, tyče</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   0232184, 0231843, 0231842, 0230301</t>
+          <t>a profily z vulkanizovaného kaučuku, jiného než tvrdého kaučuku“, podpoložka 4008 21 (z nelehčeného</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CO TO JE? Desky / pásy z vulkanizovaného kaučuku v rolích, černé, 65 ±5 ShA, 2-3 a 7-8 MPa, tl. 3–20 mm.</t>
+          <t>kaučuku – desky, listy a pásy), KN 4008 21 90 (ostatní).</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Z ČEHO TO JE? Vulkanizovaný nelehčený kaučuk SBR / EPDM; u tří položek 1 textilní vložka (fabric) jako výztuž.</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">   K ČEMU SLOUŽÍ? Technická pryž – těsnění, obklady, podložky; polotovar dodávaný v rolích k dalšímu zpracování.</t>
+          <t>Odpovídá zboží v zásilce: desky a pásy z vulkanizovaného nelehčeného kaučuku SBR / EPDM v rolích,</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Postup: TŘÍDA VII (plasty, kaučuk a pryž) → kapitola 40 → úvodní poznámky ke kap. 40 zboží nevylučují →</t>
+          <t>černé, 65 ±5 ShA, 2-3 a 7-8 MPa, tloušťka 3–20 mm, u části položek s 1 textilní vložkou (fabric)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">   číslo 4008 „Desky, listy, pásy, tyče a profily z vulkanizovaného kaučuku, jiného než tvrdého kaučuku“ →</t>
+          <t>jako výztuží – ta podle VPV 3(b) nemění podstatný charakter, ten dává kaučuk.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   podpoložka 4008 21 (z nelehčeného kaučuku – desky, listy a pásy) → KN 4008 21 90 (ostatní). VPV 1 a VPV 6.</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Textilní vložka: podle VPV 3(b) dává podstatný charakter kaučuk (výrazně převažuje hmotnostně, vložka</t>
+          <t>Pro pořádek k dohledání: u kamínkových desek (art. 0230559, 0230564) a rýhované desky (art. 0230238)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">   plní pouze vyztužovací funkci) → zůstává v kap. 40, nikoli v kap. 59.</t>
+          <t>přicházelo v úvahu také číslo 4016 91 00 „Podlahové krytiny a rohože“. Deklarant rozhodl, že celá</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>zásilka jde pod 4008 21 90 – jednotné zařazení odpovídá tomu, že zboží je dodáváno v rolích jako</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B) 4016 91 00 – art. 0230559, 0230564, 0230238</t>
+          <t>materiál, nikoli jako hotová rohož. Uvedeno pouze jako záznam o zvážené alternativě.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   CO TO JE? Podlahové rohože z pryže – kamínková deska, kamínková deska speciál, rýhovaná deska.</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Z ČEHO TO JE? Vulkanizovaný nelehčený kaučuk (pryž).</t>
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>⚠ PREFERENČNÍ PŮVOD A REX – OBOJÍ CHYBÍ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">   K ČEMU SLOUŽÍ? Podlahová krytina / rohož – stájové a protiskluzové podlahy (Horse Rubber mat, Stable Mat).</t>
+          <t>PREFERENČNÍ VĚTA: NENÍ uvedena v žádném z dokladů. Zkontrolovány obě faktury, oba packing listy i B/L.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Postup: TŘÍDA VII → kapitola 40 → číslo 4016 „Ostatní výrobky z vulkanizovaného kaučuku, jiného než</t>
+          <t>REX ČÍSLO: NENÍ na žádné z faktur uvedeno. Faktury neobsahují číslo registrovaného vývozce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">   tvrdého kaučuku“ → KN 4016 91 00 „Podlahové krytiny a rohože“. Podle VPV 3(a) má konkrétnější popis</t>
+          <t>ani jiné číslo celního povolení vývozce.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (hotová podlahová krytina) přednost před obecným číslem 4008 pro desky a pásy.</t>
+          <t>Země původu: Čína (CN). EU nemá s ČLR dohodu o preferenčním obchodu, preferenční sazba proto</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>není možná ani při doložení prohlášení – uplatní se standardní třetizemní clo (erga omnes).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>⚠ NEJISTOTA – DOPORUČUJI KONZULTOVAT</t>
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>→ Sazbu k oběma HS kódům ověřit v TARIC k datu propuštění zboží.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>1) Hranice 4008 vs. 4016 u art. 0230559 (3 mm Kamínková deska, dodávaná v roli 1,2 × 10 m) – rozměr</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   odpovídá spíše roli materiálu než hotové rohoži. Zařazeno do 4016 91 00 podle účelu (stájová rohož).</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>CBAM</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2) Položky s textilní vložkou – hranice kap. 40 vs. 5906. Zařazeno do 4008 21 90.</t>
+          <t>Zásilka NEOBSAHUJE žádnou CBAM položku – kaučuk a pryž (kapitola 40) nejsou v příloze I nařízení CBAM</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
-        <is>
-          <t>→ Před podáním doporučuji potvrdit v TARIC, případně konzultovat tarifní tým: customs.tariff@mauriceward.com</t>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>(CBAM = cement, elektřina, hnojiva, železo a ocel, hliník, vodík). Kód Y128/Y238/Y137 se na žádné JSD neuvádí.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (tento krok jsem zatím neprovedla – rozhodni prosím Ty).</t>
+          <t>Pro pořádek prověřeno v reference/CBAM_receivers_CZ.xlsx (list List1):</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>⚠ ADITEG s.r.o. (EORI CZ26905710) V REGISTRU NENÍ – ani podle názvu firmy, ani podle EORI.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="28" t="inlineStr">
-        <is>
-          <t>⚠ PREFERENČNÍ PŮVOD A REX – OBOJÍ CHYBÍ</t>
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>→ Pro tuto zásilku to nevadí (žádné CBAM zboží). Pokud by ADITEG někdy dovážel CBAM zboží, je nutné</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PREFERENČNÍ VĚTA: NENÍ uvedena v žádném z dokladů. Zkontrolovány obě faktury, oba packing listy i B/L.</t>
+          <t xml:space="preserve">   nejdřív zjistit jeho CBAM status a doplnit ho do registru. Status nedomýšlet.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>REX ČÍSLO: NENÍ na žádné z faktur uvedeno. Faktury neobsahují číslo registrovaného vývozce</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>ani jiné číslo celního povolení vývozce.</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>ANTIDUMPING</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Země původu: Čína (CN). EU nemá s ČLR dohodu o preferenčním obchodu, preferenční sazba proto</t>
+          <t>Pro desky a pásy z vulkanizovaného kaučuku (4008 21 90) původem z ČLR nebylo zjištěno žádné</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>není možná ani při doložení prohlášení – uplatní se standardní třetizemní clo (erga omnes).</t>
+          <t>platné antidumpingové ani vyrovnávací opatření. Ověřit v TARIC k datu podání JSD.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
-        <is>
-          <t>→ Sazbu k oběma HS kódům ověřit v TARIC k datu propuštění zboží.</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>INCOTERM</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>CBAM</t>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FOB Xingang (Tianjin), Čína – dle obou faktur. Na B/L „FREIGHT COLLECT“, což je s FOB v souladu.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Zásilka NEOBSAHUJE žádnou CBAM položku – kaučuk a pryž (kapitola 40) nejsou v příloze I nařízení CBAM</t>
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t>→ Do celní hodnoty je nutno připočíst náklady na přepravu a pojištění do místa vstupu do EU.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>(CBAM = cement, elektřina, hnojiva, železo a ocel, hliník, vodík). Kód Y128/Y238/Y137 se na žádné JSD neuvádí.</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Pro pořádek prověřeno v reference/CBAM_receivers_CZ.xlsx (list List1):</t>
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>⚠ NESROVNALOST V PODKLADECH – art. 0230564</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31" t="inlineStr">
-        <is>
-          <t>⚠ ADITEG s.r.o. (EORI CZ26905710) V REGISTRU NENÍ – ani podle názvu firmy, ani podle EORI.</t>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Faktura uvádí „17 mm Kamínková deska spec.“, packing list v popisu „12 mm Kamínková deska spec.“,</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29" t="inlineStr">
-        <is>
-          <t>→ Pro tuto zásilku to nevadí (žádné CBAM zboží). Pokud by ADITEG někdy dovážel CBAM zboží, je nutné</t>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>přičemž rozměr je v obou dokladech 1,22 x 1,83 m x 17 mm. V tabulce je použit popis z faktury (17 mm).</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   nejdřív zjistit jeho CBAM status a doplnit ho do registru. Status nedomýšlet.</t>
+      <c r="A89" s="29" t="inlineStr">
+        <is>
+          <t>→ Vyjasnit s odesílatelem před podáním – údaj jde do popisu zboží v kolonce 31.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Kontrola množství: 446,52 m² / (1,22 × 1,83 m) = přesně 200 ks – souhlasí s packing listem.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="30" t="inlineStr">
-        <is>
-          <t>ANTIDUMPING</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Pro desky a rohože z vulkanizovaného kaučuku (4008 21, 4016 91) původem z ČLR nebylo zjištěno</t>
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>POZNÁMKA K POPISU ZBOŽÍ A KE SLUČOVÁNÍ</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>žádné platné antidumpingové ani vyrovnávací opatření. Ověřit v TARIC k datu podání JSD.</t>
+          <t>Popisy v tabulce jsou převzaty doslovně z faktur (česky), bez úprav a bez přeformulování.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Celá zásilka má jeden HS kód 4008 21 90, na každé JSD proto vychází jediný řádek. Stejný kód je na JSD 1</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="30" t="inlineStr">
-        <is>
-          <t>INCOTERM</t>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>i na JSD 2 samostatně – jde o dvě různá celní prohlášení, nelze je slučovat napříč JSD.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
-        <is>
-          <t>FOB Xingang (Tianjin), Čína – dle obou faktur. Na B/L „FREIGHT COLLECT“, což je s FOB v souladu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="29" t="inlineStr">
-        <is>
-          <t>→ Do celní hodnoty je nutno připočíst náklady na přepravu a pojištění do místa vstupu do EU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="28" t="inlineStr">
-        <is>
-          <t>⚠ NESROVNALOST V PODKLADECH – art. 0230564</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Faktura uvádí „17 mm Kamínková deska spec.“, packing list v popisu „12 mm Kamínková deska spec.“,</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>přičemž rozměr je v obou dokladech 1,22 x 1,83 m x 17 mm. V tabulce je použit popis z faktury (17 mm).</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="29" t="inlineStr">
-        <is>
-          <t>→ Vyjasnit s odesílatelem před podáním – údaj jde do popisu zboží v kolonce 31.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Kontrola množství: 446,52 m² / (1,22 × 1,83 m) = přesně 200 ks – souhlasí s packing listem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="27" t="inlineStr">
-        <is>
-          <t>POZNÁMKA K POPISU ZBOŽÍ A KE SLUČOVÁNÍ</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Popisy v tabulce jsou převzaty doslovně z faktur (česky), bez úprav a bez přeformulování.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Položky jsou sloučeny na unikátní HS kódy v rámci každého JSD. Stejný HS kód 4008 21 90 je na JSD 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>i na JSD 2 samostatně – jde o dvě různá celní prohlášení, nelze je slučovat napříč JSD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
         <is>
           <t>Odesílatel je u celé zásilky jeden (Qingdao Conet), dělení podle odesílatele proto nebylo potřeba.</t>
         </is>

--- a/output/HS_Code_Summary_ADITEG_CZ26009365.xlsx
+++ b/output/HS_Code_Summary_ADITEG_CZ26009365.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Popis zboží (CZ) – doslovně z faktury</t>
+          <t>Popis zboží (CZ) – zkrácený</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -663,13 +663,13 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0231268 – EPDM/SBR 65 +/- 5 Sh., černá, 2-3 MPa 3 mm, 2 x 10 m
-0230179 – SBR 65 +/- 5 Sh.černá, 2-3 MPa 5 mm x 1.200 x 10.000 mm
-0231419 – SBR 65 +/- 5 Sh.černá, 2-3 MPa 6 mm x 2.000 x 10.000 mm
-0230264 – SBR 65 +/- 5 Sh.černá, 2-3 MPa, 1 vložka(fabric) 10 mm x 1.200 x 10.000 mm
-0234614 – SBR 65 +/-5SHA  černá, 2-3 MPa 8 mm x1.600 x 10.000 mm
-0230559 – 3 mm Kamínková deska.(Horse Rubber mat) 3 mm x 1.200 x 10.000 mm
-0230564 – 17 mm Kamínková deska spec.（Round button Stable Mat）Kamínková deska - speciál 1,22 x 1,83 m x 17 mm</t>
+          <t>0231268 – EPDM/SBR deska 3 mm, 2 x 10 m
+0230179 – SBR deska 5 mm x 1.200 x 10.000 mm
+0231419 – SBR deska 6 mm x 2.000 x 10.000 mm
+0230264 – SBR deska s 1 textilní vložkou 10 mm x 1.200 x 10.000 mm
+0234614 – SBR deska 8 mm x 1.600 x 10.000 mm
+0230559 – Kamínková deska 3 mm x 1.200 x 10.000 mm
+0230564 – Kamínková deska speciál 1,22 x 1,83 m x 17 mm</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -755,13 +755,13 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>0230540 – EPDM/SBR 65 +/- 5 Sh.černá, 7-8 MPa 5mm x 1.200 x 10.000 mm
-0232061 – SBR 65 +/- 5 Sh. černá, 2-3 MPa 20 mm x 1.400 x 10.000 mm
-0232184 – SBR 65+/-5SHAčerná, 2-3 MPa, 1 vložky(fabirc)3mm x 1.400 x 10.000 mm
-0231843 – SBR  65+/5SHA černá, 2-3 MPa, 10mm x 1.200 x 25.000 mm
-0231842 – SBR 65 +/- 5 Sh.černá, 2-3 MPa 10 mm x 1.200 x 13.000 mm
-0230264 – SBR 65 +/- 5 Sh. černá, 2-3 MPa, 1 vložka(fabric) 10 mm x 1.200 x 10.000 mm
-0230301 – EPDM/SBR 65 +/- 5 ShA černá, 2-3 MPa, 1 vložka 8 mm x 1.200 x 10.000 mm</t>
+          <t>0230540 – EPDM/SBR deska 5 mm x 1.200 x 10.000 mm
+0232061 – SBR deska 20 mm x 1.400 x 10.000 mm
+0232184 – SBR deska s 1 textilní vložkou 3 mm x 1.400 x 10.000 mm
+0231843 – SBR deska 10 mm x 1.200 x 25.000 mm
+0231842 – SBR deska 10 mm x 1.200 x 13.000 mm
+0230264 – SBR deska s 1 textilní vložkou 10 mm x 1.200 x 10.000 mm
+0230301 – EPDM/SBR deska s 1 textilní vložkou 8 mm x 1.200 x 10.000 mm</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>0230238 – Fine ribbed mat(Rýhovaná deska - malá) 3mm，1.2X10m</t>
+          <t>0230238 – Rýhovaná deska 3 mm, 1,2 x 10 m</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Doslovný český popis z faktury, bez úprav.</t>
+          <t>Zde zkrácený popis (materiál, provedení, rozměr). Doslovný popis z faktury je na listu „Položky (detail)“.</t>
         </is>
       </c>
       <c r="G17" s="20" t="n"/>
@@ -1978,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A96"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -2571,26 +2571,54 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Popisy v tabulce jsou převzaty doslovně z faktur (česky), bez úprav a bez přeformulování.</t>
+          <t>Popisy na listu „HS Summary“ jsou zkrácené – ponechán materiál (SBR / EPDM), provedení (deska, deska</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Celá zásilka má jeden HS kód 4008 21 90, na každé JSD proto vychází jediný řádek. Stejný kód je na JSD 1</t>
+          <t>s textilní vložkou, kamínková / rýhovaná deska) a rozměr. Vypuštěna tvrdost (65 ±5 Sh) a pevnost</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>i na JSD 2 samostatně – jde o dvě různá celní prohlášení, nelze je slučovat napříč JSD.</t>
+          <t>(2-3 / 7-8 MPa), které nejsou pro zařazení do 4008 21 90 rozhodující.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
+        <is>
+          <t>Doslovné české popisy z faktur zůstávají beze změny na listu „Položky (detail)“ – pro doložení</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>shody s fakturou při kontrole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Celá zásilka má jeden HS kód 4008 21 90, na každé JSD proto vychází jediný řádek. Stejný kód je na JSD 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>i na JSD 2 samostatně – jde o dvě různá celní prohlášení, nelze je slučovat napříč JSD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Odesílatel je u celé zásilky jeden (Qingdao Conet), dělení podle odesílatele proto nebylo potřeba.</t>
         </is>
